--- a/results/Int All Data 0.1/Rando_6_permute.xlsx
+++ b/results/Int All Data 0.1/Rando_6_permute.xlsx
@@ -440,727 +440,727 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7795452219700071</v>
+        <v>0.7745797361664124</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7795452219700071</v>
+        <v>0.7738157258214564</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7795452219700071</v>
+        <v>0.7797370967141741</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7795452219700071</v>
+        <v>0.7797847746809066</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.794011414802962</v>
+        <v>0.7792824117143602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7947277471811856</v>
+        <v>0.7792824117143602</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7960406355821829</v>
+        <v>0.7853712369292598</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7960406355821829</v>
+        <v>0.7890959327205745</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7949661370148476</v>
+        <v>0.7890959327205745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7946079708257359</v>
+        <v>0.7912926078219775</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7949661370148476</v>
+        <v>0.7887377665314628</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7960406355821829</v>
+        <v>0.7887377665314628</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7947033267592007</v>
+        <v>0.778876567558516</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7899041324005507</v>
+        <v>0.7790916998474304</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7906204647787742</v>
+        <v>0.7787335336583188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7919333531797714</v>
+        <v>0.7762263703345365</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7952998827819744</v>
+        <v>0.7762263703345365</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7943684181148365</v>
+        <v>0.7780416217020802</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7947265843039482</v>
+        <v>0.7780416217020802</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7886621795110333</v>
+        <v>0.7780416217020802</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7887098574777658</v>
+        <v>0.779569642391992</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7894261898559893</v>
+        <v>0.7787812116250512</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7902378781676775</v>
+        <v>0.7784230454359394</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7902378781676775</v>
+        <v>0.7770368957689875</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7900227458787631</v>
+        <v>0.7763449838127489</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7883749488334015</v>
+        <v>0.7751751293119489</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7908576917351988</v>
+        <v>0.7733842983663901</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7908576917351988</v>
+        <v>0.7691816600305139</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7947730993934432</v>
+        <v>0.7717365013210284</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7904995255460872</v>
+        <v>0.778421882558702</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7916693800468872</v>
+        <v>0.779090536970193</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7963964760168198</v>
+        <v>0.7794487031593049</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7971128083950434</v>
+        <v>0.7782311706917724</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7963487980500874</v>
+        <v>0.7799975812153462</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7963487980500874</v>
+        <v>0.7791382149369255</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7963011200833551</v>
+        <v>0.773647108622037</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7958475979607784</v>
+        <v>0.7719039556432107</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7916693800468872</v>
+        <v>0.7696351821530905</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.793460210992446</v>
+        <v>0.7705666468202286</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7800673538495888</v>
+        <v>0.7748646410895694</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7788730789268039</v>
+        <v>0.7765368585569159</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.782837327429018</v>
+        <v>0.778446302980687</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7817151508949504</v>
+        <v>0.772644708443419</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.784269992185465</v>
+        <v>0.764289435492874</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7832908495515944</v>
+        <v>0.7572226305213412</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7706620027536932</v>
+        <v>0.761090360212853</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7722853793770699</v>
+        <v>0.7616404011461317</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7624672068619061</v>
+        <v>0.7542631079522197</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7624672068619061</v>
+        <v>0.7542631079522197</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7551852696014587</v>
+        <v>0.727237840955606</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7539909946786738</v>
+        <v>0.7292670617348267</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7516257023778514</v>
+        <v>0.726235440776988</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7452752297845422</v>
+        <v>0.7242550608417371</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7449170635954303</v>
+        <v>0.7249713932199606</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7490952815093216</v>
+        <v>0.7276936888326573</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7569981952145276</v>
+        <v>0.735286114315484</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7641615189967625</v>
+        <v>0.7187651174040859</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7564993208796934</v>
+        <v>0.7176906188367507</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7532048896662077</v>
+        <v>0.7242306404197523</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7509605365980725</v>
+        <v>0.7122227700666096</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7354186823205449</v>
+        <v>0.7167312451159156</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7348453838425184</v>
+        <v>0.6999474379488706</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7361361775760057</v>
+        <v>0.7149625088378671</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7369001879209616</v>
+        <v>0.7135740334164403</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7409353719346556</v>
+        <v>0.712570470360585</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7429169147471439</v>
+        <v>0.7054780820898299</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7445635489152681</v>
+        <v>0.7081759572805417</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7437518606035798</v>
+        <v>0.6942063130279462</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7418412533025713</v>
+        <v>0.6958738789863432</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7418168328805865</v>
+        <v>0.7011021750455848</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7418168328805865</v>
+        <v>0.7066177017824582</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7515582554980835</v>
+        <v>0.7074293900941465</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7537072526327541</v>
+        <v>0.7091469597737505</v>
       </c>
     </row>
     <row r="75">
@@ -1170,267 +1170,267 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7528967271983031</v>
+        <v>0.7143531611654821</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7448496167156626</v>
+        <v>0.6943691158411789</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7452077829047743</v>
+        <v>0.6940109496520672</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7294973114278271</v>
+        <v>0.6839834592341756</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7323382205187363</v>
+        <v>0.6548033807167045</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.732696386707848</v>
+        <v>0.655519713094928</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7309299761842742</v>
+        <v>0.6335750567484092</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7038023759907714</v>
+        <v>0.633933222937521</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6980717169649835</v>
+        <v>0.621778830052469</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6906955866483088</v>
+        <v>0.6033937409295576</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6983356900978678</v>
+        <v>0.6040147173743162</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6966146317865516</v>
+        <v>0.6061392940870018</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6878023480817177</v>
+        <v>0.6172412830722286</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6736419919621925</v>
+        <v>0.6157144252595541</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6775818200424217</v>
+        <v>0.6053520261972984</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6771992334313252</v>
+        <v>0.6102709969113981</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6771992334313252</v>
+        <v>0.6091046310423102</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6766026774085513</v>
+        <v>0.6250046515089496</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6384451866185391</v>
+        <v>0.5963292617124996</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6433641573326387</v>
+        <v>0.5959710955233878</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6381114408514121</v>
+        <v>0.5788988948014736</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6421466248651062</v>
+        <v>0.5937988408439698</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6358438302385294</v>
+        <v>0.5825491664495962</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6347693316711942</v>
+        <v>0.5789442470137313</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4987347895657351</v>
+        <v>0.5789442470137313</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4983766233766234</v>
+        <v>0.5780837178580731</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4986871115990027</v>
+        <v>0.6056846090871879</v>
       </c>
     </row>
     <row r="102">
@@ -1440,473 +1440,473 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4990929557548469</v>
+        <v>0.5995957838722882</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4990929557548469</v>
+        <v>0.6101256372567261</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4990452777881145</v>
+        <v>0.5332617776206602</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5002628102556469</v>
+        <v>0.5343839541547278</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4982812674431585</v>
+        <v>0.5053724928366762</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4982812674431585</v>
+        <v>0.505730659025788</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4986871115990027</v>
+        <v>0.5032234957020058</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4986871115990027</v>
+        <v>0.5032234957020058</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4991406337215793</v>
+        <v>0.5032234957020058</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4974219011647379</v>
+        <v>0.5007163323782235</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4929820358724371</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4929820358724371</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4929820358724371</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.495655490641164</v>
+        <v>0.5010744985673352</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4952496464853198</v>
+        <v>0.5010744985673352</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4952973244520523</v>
+        <v>0.5010744985673352</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4952973244520523</v>
+        <v>0.5010744985673352</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4944379581736315</v>
+        <v>0.5007163323782235</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4952496464853198</v>
+        <v>0.4990452777881145</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4999523220332676</v>
+        <v>0.499498799910691</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4999523220332676</v>
+        <v>0.499498799910691</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4982812674431585</v>
+        <v>0.4987824675324675</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4986871115990027</v>
+        <v>0.4990929557548469</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.496156690730473</v>
+        <v>0.4987824675324675</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4969207010754289</v>
+        <v>0.4987824675324675</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4924087373944108</v>
+        <v>0.4987824675324675</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4935309139284784</v>
+        <v>0.4987824675324675</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4992127321102966</v>
+        <v>0.4987824675324675</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4992127321102966</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4992127321102966</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4992127321102966</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4979951996427641</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4979475216760317</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4988545659211849</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4988545659211849</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4993557660104938</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4993557660104938</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4993557660104938</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.498997599821382</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.498997599821382</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4995464778774235</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4995464778774235</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4995464778774235</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4995464778774235</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4999523220332676</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4999046440665352</v>
+        <v>0.4995941558441558</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4999046440665352</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B156" t="n">
